--- a/artfynd/A 3173-2023 artfynd.xlsx
+++ b/artfynd/A 3173-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3173-2023 artfynd.xlsx
+++ b/artfynd/A 3173-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>106832231</v>
       </c>
       <c r="B2" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -726,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583496.8216765365</v>
+        <v>583497</v>
       </c>
       <c r="R2" t="n">
-        <v>6403328.916016363</v>
+        <v>6403329</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -799,51 +794,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>106832513</v>
+        <v>106832423</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -851,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583637.325421087</v>
+        <v>583567</v>
       </c>
       <c r="R3" t="n">
-        <v>6403333.964584557</v>
+        <v>6403357</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -886,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -924,15 +913,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>106832423</v>
+        <v>107226804</v>
       </c>
       <c r="B4" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -959,7 +943,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -971,14 +955,14 @@
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>A 3173, Fälgars mosse N, Sm</t>
+          <t>A 2518, Dröppshult, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>583567.3441699134</v>
+        <v>583629</v>
       </c>
       <c r="R4" t="n">
-        <v>6403357.058484806</v>
+        <v>6403364</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1005,22 +989,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10:00</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-02-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>13:00</t>
+          <t>2023-03-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1041,7 +1015,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+          <t>Magnus Kasselstrand</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1051,12 +1025,7 @@
         <v>107226900</v>
       </c>
       <c r="B5" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1099,10 +1068,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>583495.2554781206</v>
+        <v>583495</v>
       </c>
       <c r="R5" t="n">
-        <v>6403352.895919361</v>
+        <v>6403353</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,19 +1101,9 @@
           <t>2023-03-10</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-10</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1175,12 +1134,7 @@
         <v>107226914</v>
       </c>
       <c r="B6" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,10 +1177,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583494.1866779221</v>
+        <v>583494</v>
       </c>
       <c r="R6" t="n">
-        <v>6403352.87377085</v>
+        <v>6403353</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1256,19 +1210,9 @@
           <t>2023-03-10</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-03-10</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1296,15 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107226804</v>
+        <v>107226925</v>
       </c>
       <c r="B7" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1270,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1347,10 +1286,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583629.2238116207</v>
+        <v>583723</v>
       </c>
       <c r="R7" t="n">
-        <v>6403363.678457662</v>
+        <v>6403418</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1380,19 +1319,9 @@
           <t>2023-03-10</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-03-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1420,61 +1349,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107226925</v>
+        <v>106830953</v>
       </c>
       <c r="B8" t="n">
-        <v>89412</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>A 2518, Dröppshult, Sm</t>
+          <t>Ljusgöl V, Dröppshult, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583722.7262185033</v>
+        <v>583654</v>
       </c>
       <c r="R8" t="n">
-        <v>6403417.913373172</v>
+        <v>6403487</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1501,22 +1422,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2023-02-16</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-03-10</t>
+          <t>2023-02-16</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1525,7 +1446,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1537,10 +1457,120 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>106832513</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>A 3173, Fälgars mosse N, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>583637</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6403334</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Törnsfall</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-02-16</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
           <t>Magnus Kasselstrand</t>
         </is>
       </c>
-      <c r="AY8" t="inlineStr"/>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand, Ingvor Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
